--- a/artfynd/A 22410-2026 artfynd.xlsx
+++ b/artfynd/A 22410-2026 artfynd.xlsx
@@ -882,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134404553</v>
+        <v>134404057</v>
       </c>
       <c r="B4" t="n">
-        <v>8460</v>
+        <v>8449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563983</v>
+        <v>564131</v>
       </c>
       <c r="R4" t="n">
-        <v>6448530</v>
+        <v>6448453</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134404057</v>
+        <v>134404553</v>
       </c>
       <c r="B5" t="n">
-        <v>8449</v>
+        <v>8460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564131</v>
+        <v>563983</v>
       </c>
       <c r="R5" t="n">
-        <v>6448453</v>
+        <v>6448530</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1198,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134404063</v>
+        <v>134404593</v>
       </c>
       <c r="B7" t="n">
-        <v>5181</v>
+        <v>106310</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,32 +1209,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1242,10 +1237,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564075</v>
+        <v>563900</v>
       </c>
       <c r="R7" t="n">
-        <v>6448493</v>
+        <v>6448542</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134404593</v>
+        <v>134404063</v>
       </c>
       <c r="B8" t="n">
-        <v>106310</v>
+        <v>5181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1316,27 +1311,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563900</v>
+        <v>564075</v>
       </c>
       <c r="R8" t="n">
-        <v>6448542</v>
+        <v>6448493</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134404585</v>
+        <v>134404594</v>
       </c>
       <c r="B11" t="n">
         <v>5201</v>
@@ -1659,10 +1659,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563934</v>
+        <v>563849</v>
       </c>
       <c r="R11" t="n">
-        <v>6448537</v>
+        <v>6448582</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134404594</v>
+        <v>134404585</v>
       </c>
       <c r="B12" t="n">
         <v>5201</v>
@@ -1766,10 +1766,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563849</v>
+        <v>563934</v>
       </c>
       <c r="R12" t="n">
-        <v>6448582</v>
+        <v>6448537</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 22410-2026 artfynd.xlsx
+++ b/artfynd/A 22410-2026 artfynd.xlsx
@@ -783,7 +783,7 @@
         <v>134404126</v>
       </c>
       <c r="B3" t="n">
-        <v>96615</v>
+        <v>96622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134404057</v>
+        <v>134404553</v>
       </c>
       <c r="B4" t="n">
-        <v>8449</v>
+        <v>8460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564131</v>
+        <v>563983</v>
       </c>
       <c r="R4" t="n">
-        <v>6448453</v>
+        <v>6448530</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134404553</v>
+        <v>134404057</v>
       </c>
       <c r="B5" t="n">
-        <v>8460</v>
+        <v>8449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +1000,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563983</v>
+        <v>564131</v>
       </c>
       <c r="R5" t="n">
-        <v>6448530</v>
+        <v>6448453</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
         <v>134404590</v>
       </c>
       <c r="B6" t="n">
-        <v>96409</v>
+        <v>96416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>134404593</v>
       </c>
       <c r="B7" t="n">
-        <v>106310</v>
+        <v>106317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134404579</v>
+        <v>134404572</v>
       </c>
       <c r="B9" t="n">
-        <v>92356</v>
+        <v>98053</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1418,26 +1418,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4217</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1445,10 +1446,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563938</v>
+        <v>563949</v>
       </c>
       <c r="R9" t="n">
-        <v>6448537</v>
+        <v>6448545</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,11 +1482,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På tall.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1513,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134404572</v>
+        <v>134404579</v>
       </c>
       <c r="B10" t="n">
-        <v>98046</v>
+        <v>92363</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1524,27 +1520,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>4217</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1552,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563949</v>
+        <v>563938</v>
       </c>
       <c r="R10" t="n">
-        <v>6448545</v>
+        <v>6448537</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1588,6 +1583,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1832,7 +1832,7 @@
         <v>134404554</v>
       </c>
       <c r="B13" t="n">
-        <v>97421</v>
+        <v>97428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 22410-2026 artfynd.xlsx
+++ b/artfynd/A 22410-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134404595</v>
+        <v>134404554</v>
       </c>
       <c r="B2" t="n">
-        <v>57972</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563840</v>
+        <v>563964</v>
       </c>
       <c r="R2" t="n">
-        <v>6448569</v>
+        <v>6448557</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,6 +758,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -783,7 +780,7 @@
         <v>134404126</v>
       </c>
       <c r="B3" t="n">
-        <v>96622</v>
+        <v>96629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134404553</v>
+        <v>134404590</v>
       </c>
       <c r="B4" t="n">
-        <v>8460</v>
+        <v>96423</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,32 +890,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -926,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563983</v>
+        <v>563930</v>
       </c>
       <c r="R4" t="n">
-        <v>6448530</v>
+        <v>6448558</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134404057</v>
+        <v>134403932</v>
       </c>
       <c r="B5" t="n">
-        <v>8449</v>
+        <v>96410</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,32 +992,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>2812</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1033,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564131</v>
+        <v>564134</v>
       </c>
       <c r="R5" t="n">
-        <v>6448453</v>
+        <v>6448450</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134404590</v>
+        <v>134404579</v>
       </c>
       <c r="B6" t="n">
-        <v>96416</v>
+        <v>92370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1107,27 +1094,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2810</v>
+        <v>4217</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1135,10 +1121,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563930</v>
+        <v>563938</v>
       </c>
       <c r="R6" t="n">
-        <v>6448558</v>
+        <v>6448537</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,6 +1157,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134404593</v>
+        <v>134403571</v>
       </c>
       <c r="B7" t="n">
-        <v>106317</v>
+        <v>92385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,27 +1200,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1237,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563900</v>
+        <v>564146</v>
       </c>
       <c r="R7" t="n">
-        <v>6448542</v>
+        <v>6448453</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,10 +1290,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134404063</v>
+        <v>134404548</v>
       </c>
       <c r="B8" t="n">
-        <v>5181</v>
+        <v>57972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1311,30 +1301,29 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1344,10 +1333,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564075</v>
+        <v>564055</v>
       </c>
       <c r="R8" t="n">
-        <v>6448493</v>
+        <v>6448522</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,7 +1377,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1407,10 +1395,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134404572</v>
+        <v>134404595</v>
       </c>
       <c r="B9" t="n">
-        <v>98053</v>
+        <v>57972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1418,27 +1406,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1446,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563949</v>
+        <v>563840</v>
       </c>
       <c r="R9" t="n">
-        <v>6448545</v>
+        <v>6448569</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,7 +1482,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1509,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134404579</v>
+        <v>134404063</v>
       </c>
       <c r="B10" t="n">
-        <v>92363</v>
+        <v>5181</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1520,26 +1511,32 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4217</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1547,10 +1544,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563938</v>
+        <v>564075</v>
       </c>
       <c r="R10" t="n">
-        <v>6448537</v>
+        <v>6448493</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1583,11 +1580,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-06-14</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1615,7 +1607,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134404594</v>
+        <v>134404585</v>
       </c>
       <c r="B11" t="n">
         <v>5201</v>
@@ -1659,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563849</v>
+        <v>563934</v>
       </c>
       <c r="R11" t="n">
-        <v>6448582</v>
+        <v>6448537</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,7 +1714,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134404585</v>
+        <v>134404594</v>
       </c>
       <c r="B12" t="n">
         <v>5201</v>
@@ -1766,10 +1758,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563934</v>
+        <v>563849</v>
       </c>
       <c r="R12" t="n">
-        <v>6448537</v>
+        <v>6448582</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,38 +1821,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134404554</v>
+        <v>134404553</v>
       </c>
       <c r="B13" t="n">
-        <v>97428</v>
+        <v>8460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1868,10 +1865,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563964</v>
+        <v>563983</v>
       </c>
       <c r="R13" t="n">
-        <v>6448557</v>
+        <v>6448530</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,6 +1925,419 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134404057</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>St. Solliden, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>564131</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6448453</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134404593</v>
+      </c>
+      <c r="B15" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>St. Solliden, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>563900</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6448542</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134404572</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>St. Solliden, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>563949</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6448545</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134404597</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>St. Solliden, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>563805</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6448553</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Emil Lindgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22410-2026 artfynd.xlsx
+++ b/artfynd/A 22410-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134404554</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134404126</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134404590</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134404579</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134404548</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134404595</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134404063</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134404585</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1615,6 +1660,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134404594</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134404553</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1824,6 +1879,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134404593</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1926,6 +1986,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134404572</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2028,6 +2093,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134404597</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2130,6 +2200,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134403932</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2231,6 +2306,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134403571</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2338,8 +2418,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134404057</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>